--- a/flood re.xlsx
+++ b/flood re.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gwd.grpinf.net\AWSCloudDesktop\test-homedrives\AAJO.GWD\Desktop\DL-GOCO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gwd.grpinf.net\AWSCloudDesktop\test-homedrives\AAJO.GWD\Desktop\DL CTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{497404A9-288D-4D7B-BAC6-EE35B61DB6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3A4303B-4C40-4F14-8023-D5DEC22E4626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13530" xr2:uid="{0B503D3C-84C1-455B-966F-A97CF04F07E0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13530" xr2:uid="{7A1C6CA2-399D-4391-A9B3-437C5B3907DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,16 +98,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>77742</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>67163</xdr:rowOff>
+      <xdr:colOff>487374</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57477</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89988FBD-F479-2260-2317-88E9112D5213}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DA4596F-903F-6283-8BA1-DF881AFB8945}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -124,95 +124,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="11050542" cy="3496163"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>468492</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>85976</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B34EA352-6475-D9BC-9E82-F19BBCFE17C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="4000500"/>
-          <a:ext cx="12660492" cy="1800476"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>334953</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>133794</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0042357-9CB9-55DE-B367-FF3E48744F29}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6286500"/>
-          <a:ext cx="11307753" cy="3181794"/>
+          <a:ext cx="11460174" cy="2343477"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -540,7 +452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D193946C-DC9E-461E-AACA-B80027503367}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E78ECD97-5EB6-4DF6-A6A4-7CF08C7475BA}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
